--- a/site/exports/fdu-philosophy.xlsx
+++ b/site/exports/fdu-philosophy.xlsx
@@ -14,11 +14,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'导师'!$A$1:$L$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -453,8 +453,8 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="65" customWidth="1" min="6" max="6"/>
     <col width="65" customWidth="1" min="7" max="7"/>
-    <col width="26.6" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="40.59999999999999" customWidth="1" min="8" max="8"/>
+    <col width="23.8" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
@@ -477,7 +477,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>官方主页</t>
+          <t>个人主页／职业网站（来源类型见说明）</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -487,7 +487,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>缺项与冲突</t>
+          <t>来源说明与待核事项</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -502,7 +502,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>替代官方职业报道（非个人主页）</t>
+          <t>替代职业资料来源（非已核个人主页）</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -622,11 +622,119 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>王聚</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>校区未标注</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>哲学学院</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>https://philosophy.fudan.edu.cn/64/85/c14253a222341/page.htm</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>未知（来源日期异常）</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>个人页及目录不认证实时任职；未核验原始学位证书、论文或出版社书目。；未发现本人导师的明确记录；博士生导师、博士后合作导师为指导资格，不是本人师承。；来源差异/限制：个人页记2025.12起教授；目录仍列副教授。保留差异，不判定实时职称。</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>官方资料（原来源）；公开个人页（访问与内容时效见来源记录）</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>fdu</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>复旦大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>徐波</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>校区未标注</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>哲学学院</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>https://philosophy.fudan.edu.cn/64/80/c14253a222336/page.htm</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>未知（来源日期异常）</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>个人页及目录不认证实时任职；未核验原始学位证书、论文或出版社书目。；未发现本人导师的明确记录；博士生导师、博士后合作导师为指导资格，不是本人师承。；来源差异/限制：中文工作经历记2025起教授；英文工作经历仍写2019-present Associate Professor；目录列副教授。保留差异，不判定实时职称。；来源记载职业信息：指导他人的资格：职称：博士生导师；来源记载起点：2021.12；该资格为指导他人，不是本人导师关系。上述为留存来源职业表述，不作本轮当前任职或资格认证；指导他人的资格不新增本人导师关系。</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>官方资料（原来源）；公开个人页（访问与内容时效见来源记录）</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>fdu</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>复旦大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K3"/>
+  <autoFilter ref="A1:K5"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -638,15 +746,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S15"/>
+  <dimension ref="A1:S30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="40.59999999999999" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="19.6" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
@@ -720,7 +828,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>确证授位</t>
+          <t>来源记载学位</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
@@ -1649,8 +1757,967 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>王聚</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>education_background</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>哲学学士</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>复旦大学</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2006-09</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2010-07</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr"/>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源department：哲学院</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr"/>
+      <c r="Q16" s="3" t="inlineStr">
+        <is>
+          <t>https://philosophy.fudan.edu.cn/64/85/c14253a222341/page.htm</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>fdu</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>复旦大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>王聚</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>education_background</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>科学技术哲学硕士</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>复旦大学</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2010-09</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2013-07</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr"/>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源department：哲学院</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr"/>
+      <c r="Q17" s="3" t="inlineStr">
+        <is>
+          <t>https://philosophy.fudan.edu.cn/64/85/c14253a222341/page.htm</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>fdu</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>复旦大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>王聚</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>哲学博士</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>爱丁堡大学</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>2013-09</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>2016-11</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr"/>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源department：哲学、心理学与语言科学院；来源记载（学位获授年份）：2016</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" s="3" t="inlineStr">
+        <is>
+          <t>https://philosophy.fudan.edu.cn/64/85/c14253a222341/page.htm</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>fdu</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>复旦大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>王聚</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>讲师</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>复旦大学</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>2016-12</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>2020-11</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr"/>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr"/>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>任职按留存来源表述保留；不据此认证当前人事状态。</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr"/>
+      <c r="Q19" s="3" t="inlineStr">
+        <is>
+          <t>https://philosophy.fudan.edu.cn/64/85/c14253a222341/page.htm</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>fdu</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>复旦大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>王聚</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>副教授、硕士生导师</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>复旦大学</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2020-12</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>2023-11</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr"/>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr"/>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>任职按留存来源表述保留；不据此认证当前人事状态。</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr"/>
+      <c r="Q20" s="3" t="inlineStr">
+        <is>
+          <t>https://philosophy.fudan.edu.cn/64/85/c14253a222341/page.htm</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>fdu</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>复旦大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>王聚</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>副教授、博士生导师</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>复旦大学</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>2023-11</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr"/>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr"/>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>任职按留存来源表述保留；不据此认证当前人事状态。</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr"/>
+      <c r="Q21" s="3" t="inlineStr">
+        <is>
+          <t>https://philosophy.fudan.edu.cn/64/85/c14253a222341/page.htm</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>fdu</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>复旦大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>王聚</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>教授、博士生导师、博士后合作导师</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>复旦大学</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>source-present</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr"/>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>任职按留存来源表述保留；不据此认证当前人事状态。</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr"/>
+      <c r="Q22" s="3" t="inlineStr">
+        <is>
+          <t>https://philosophy.fudan.edu.cn/64/85/c14253a222341/page.htm</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>fdu</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>复旦大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>徐波</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>哲学博士</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>香港科技大学</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr"/>
+      <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源department：人文学部</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr"/>
+      <c r="Q23" s="3" t="inlineStr">
+        <is>
+          <t>https://philosophy.fudan.edu.cn/64/80/c14253a222336/page.htm</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>fdu</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>复旦大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>徐波</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>哲学硕士</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>复旦大学</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源department：哲学学院</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr"/>
+      <c r="Q24" s="3" t="inlineStr">
+        <is>
+          <t>https://philosophy.fudan.edu.cn/64/80/c14253a222336/page.htm</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>fdu</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>复旦大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>徐波</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>学士</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>南开大学</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr"/>
+      <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源department：哲学系；来源列明学位：哲学学士；管理学学士。各原表述并列保留，不另推授位日期或将合述记录拆分。</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr"/>
+      <c r="Q25" s="3" t="inlineStr">
+        <is>
+          <t>https://philosophy.fudan.edu.cn/64/80/c14253a222336/page.htm</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>fdu</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>复旦大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>徐波</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>education_background</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>博士后、助理研究员</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>浙江大学</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr"/>
+      <c r="Q26" s="3" t="inlineStr">
+        <is>
+          <t>https://philosophy.fudan.edu.cn/64/80/c14253a222336/page.htm</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>fdu</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>复旦大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>徐波</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>education_background</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>访问学人（Visiting Researcher）</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>美国波士顿大学</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr"/>
+      <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr"/>
+      <c r="Q27" s="3" t="inlineStr">
+        <is>
+          <t>https://philosophy.fudan.edu.cn/64/80/c14253a222336/page.htm</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>fdu</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>复旦大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>徐波</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>教授</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>复旦大学</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>source-present</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>任职按留存来源表述保留；不据此认证当前人事状态。</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr"/>
+      <c r="Q28" s="3" t="inlineStr">
+        <is>
+          <t>https://philosophy.fudan.edu.cn/64/80/c14253a222336/page.htm</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>fdu</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>复旦大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>徐波</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>副教授</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>复旦大学</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr"/>
+      <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>任职按留存来源表述保留；不据此认证当前人事状态。</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr"/>
+      <c r="Q29" s="3" t="inlineStr">
+        <is>
+          <t>https://philosophy.fudan.edu.cn/64/80/c14253a222336/page.htm</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>fdu</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>复旦大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>徐波</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>讲师</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>复旦大学</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr"/>
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>任职按留存来源表述保留；不据此认证当前人事状态。</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr"/>
+      <c r="Q30" s="3" t="inlineStr">
+        <is>
+          <t>https://philosophy.fudan.edu.cn/64/80/c14253a222336/page.htm</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>fdu</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>复旦大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S15"/>
+  <autoFilter ref="A1:S30"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q3" r:id="rId2"/>
@@ -1666,6 +2733,21 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q30" r:id="rId29"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1915,18 +2997,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="25.2" customWidth="1" min="2" max="2"/>
+    <col width="33.59999999999999" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="65" customWidth="1" min="5" max="5"/>
     <col width="36.4" customWidth="1" min="6" max="6"/>
     <col width="65" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="65" customWidth="1" min="9" max="9"/>
     <col width="65" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
@@ -2170,13 +3252,229 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>王聚</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>当代知识论导论</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D6" s="2" t="inlineStr"/>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>https://philosophy.fudan.edu.cn/64/85/c14253a222341/page.htm</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>book</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>https://philosophy.fudan.edu.cn/64/85/c14253a222341/page.htm</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；source_attributed_recovery_not_reverified</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；来源person_role：author</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>fdu</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>复旦大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>王聚</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>无限主义与人类知识</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D7" s="2" t="inlineStr"/>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>https://philosophy.fudan.edu.cn/64/85/c14253a222341/page.htm</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>book</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>https://philosophy.fudan.edu.cn/64/85/c14253a222341/page.htm</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；source_attributed_recovery_not_reverified</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；来源person_role：author</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>fdu</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>复旦大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>徐波</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>由湍水之喻到幽暗意识：理学视域下的人性善恶论新探</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D8" s="2" t="inlineStr"/>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>https://philosophy.fudan.edu.cn/64/80/c14253a222336/page.htm</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>book</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>https://philosophy.fudan.edu.cn/64/80/c14253a222336/page.htm</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；source_attributed_recovery_not_reverified</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；来源person_role：author</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>fdu</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>复旦大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>徐波</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>现代儒学第六辑·儒学的多维发展</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="D9" s="2" t="inlineStr"/>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>https://philosophy.fudan.edu.cn/64/80/c14253a222336/page.htm</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>book</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>https://philosophy.fudan.edu.cn/64/80/c14253a222336/page.htm</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；source_attributed_recovery_not_reverified</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；来源person_role：editor-in-chief</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>fdu</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>复旦大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L5"/>
+  <autoFilter ref="A1:L9"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2188,14 +3486,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="46.2" customWidth="1" min="2" max="2"/>
+    <col width="57.4" customWidth="1" min="2" max="2"/>
     <col width="65" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="65" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
@@ -2501,8 +3799,156 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>王聚</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-fdu-wangju-s001-83f7930a6087</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>https://philosophy.fudan.edu.cn/64/85/c14253a222341/page.htm</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T05:00:18Z</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>fdu</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>复旦大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>王聚</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-fdu-wangju-s002-4453249c1e64</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>https://philosophy.fudan.edu.cn/36646/list.htm</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T05:01:54Z</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>fdu</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>复旦大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>徐波</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-fdu-xubo-s001-0702343af01e</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>https://philosophy.fudan.edu.cn/64/80/c14253a222336/page.htm</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T05:00:18Z</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>fdu</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>复旦大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>徐波</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-fdu-xubo-s002-4453249c1e64</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>https://philosophy.fudan.edu.cn/36646/list.htm</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T05:01:54Z</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>fdu</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>复旦大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G9"/>
+  <autoFilter ref="A1:G13"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
@@ -2512,6 +3958,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/exports/fdu-philosophy.xlsx
+++ b/site/exports/fdu-philosophy.xlsx
@@ -1794,7 +1794,7 @@
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr"/>
@@ -1859,7 +1859,7 @@
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr"/>
@@ -2302,7 +2302,7 @@
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L24" s="2" t="b">
@@ -2369,7 +2369,7 @@
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L25" s="2" t="b">
@@ -2436,7 +2436,7 @@
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L26" s="2" t="b">
